--- a/Outputs/Scenarios/PtX_demand_ES_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_ES_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001803265043043054</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03229580491692496</v>
+        <v>0.01785131107648858</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01076526830564165</v>
+        <v>0.02518252131620379</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>2.598199685446796e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.01076526830564165</v>
+        <v>0.01079250913551591</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002669514355199396</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1740791775914921</v>
+        <v>0.09622121384243575</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.05802639253049736</v>
+        <v>0.1357375241670357</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0001405007555368104</v>
       </c>
       <c r="K42" t="n">
-        <v>0.05802639253049736</v>
+        <v>0.05817322464301532</v>
       </c>
     </row>
     <row r="43">
